--- a/3-Calculations-Files/Sensors_Mapping/sensors mapping.xlsx
+++ b/3-Calculations-Files/Sensors_Mapping/sensors mapping.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javiercamacho/Desktop/Industrial PhD/Projects/VH2D-DataAnalysis/3-Calculations-Files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/javiercamacho/Desktop/Industrial PhD/Projects/VH2D-DataAnalysis/3-Calculations-Files/Sensors_Mapping/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{301A751C-761F-4E46-99A9-AF1BEEBBA39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE73B79-FEBA-C249-9E42-3DBA9DF41353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="540" windowWidth="22280" windowHeight="16420" xr2:uid="{0F907A58-12D0-425A-85FA-4500C8CE6C97}"/>
+    <workbookView xWindow="0" yWindow="520" windowWidth="26240" windowHeight="16440" xr2:uid="{0F907A58-12D0-425A-85FA-4500C8CE6C97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sensors mapping" sheetId="3" r:id="rId1"/>
     <sheet name="Volume of the chamber" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
